--- a/diseases/d025/1990-1994.xlsx
+++ b/diseases/d025/1990-1994.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>7</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>46</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>18</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>35</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>14</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>13</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>45</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>13</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>42</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>6</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>16</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>32</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>11</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>16</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>47</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>13</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>17</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>45</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>17</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>17</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>41</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>16</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>8</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>33</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>11</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>16</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>51</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>14</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>16</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>35</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>18</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>10</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>40</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>19</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>18</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>32</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>15</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>10</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>39</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>18</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>10</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>28</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>14</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>13</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>47</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>12</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>5</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20022,9 +19875,6 @@
       <c r="O100" t="n">
         <v>33</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20415,9 +20265,6 @@
       <c r="O102" t="n">
         <v>13</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20808,9 +20655,6 @@
       <c r="O104" t="n">
         <v>16</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21201,9 +21045,6 @@
       <c r="O106" t="n">
         <v>32</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21594,9 +21435,6 @@
       <c r="O108" t="n">
         <v>20</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21987,9 +21825,6 @@
       <c r="O110" t="n">
         <v>17</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22380,9 +22215,6 @@
       <c r="O112" t="n">
         <v>29</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22773,9 +22605,6 @@
       <c r="O114" t="n">
         <v>15</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23166,9 +22995,6 @@
       <c r="O116" t="n">
         <v>11</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23559,9 +23385,6 @@
       <c r="O118" t="n">
         <v>30</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23951,9 +23774,6 @@
       </c>
       <c r="O120" t="n">
         <v>15</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>

--- a/diseases/d025/1990-1994.xlsx
+++ b/diseases/d025/1990-1994.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>2014</v>
       </c>
       <c r="O2" t="n">
-        <v>7</v>
+        <v>2014</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -810,42 +810,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -916,29 +916,29 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>2014</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>2014</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1044,42 +1044,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1141,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1990-02-01</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1990-02</t>
+          <t>1990-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1185,17 +1185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1297,19 +1302,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1990-02-01</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1990-02</t>
+          <t>1990-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1419,17 +1424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1531,19 +1541,19 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1990-03-01</t>
+          <t>1990-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1990-03</t>
+          <t>1990-02</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1567,7 +1577,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1575,17 +1585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1687,19 +1702,19 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1990-03-01</t>
+          <t>1990-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1990-03</t>
+          <t>1990-02</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1801,7 +1816,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1809,17 +1824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1921,19 +1941,19 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1990-04-01</t>
+          <t>1990-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1990-04</t>
+          <t>1990-03</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1957,7 +1977,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1965,17 +1985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2077,19 +2102,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1990-04-01</t>
+          <t>1990-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1990-04</t>
+          <t>1990-03</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -2191,7 +2216,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2199,17 +2224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2311,19 +2341,19 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1990-05-01</t>
+          <t>1990-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1990-05</t>
+          <t>1990-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2347,7 +2377,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2355,17 +2385,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2467,19 +2502,19 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1990-05-01</t>
+          <t>1990-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1990-05</t>
+          <t>1990-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2581,7 +2616,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2589,17 +2624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2701,19 +2741,19 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1990-06-01</t>
+          <t>1990-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1990-06</t>
+          <t>1990-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2737,7 +2777,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2745,17 +2785,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2857,19 +2902,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1990-06-01</t>
+          <t>1990-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1990-06</t>
+          <t>1990-05</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2971,7 +3016,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -2979,17 +3024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3091,19 +3141,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1990-07-01</t>
+          <t>1990-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1990-07</t>
+          <t>1990-06</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3127,7 +3177,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -3135,17 +3185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -3247,19 +3302,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1990-07-01</t>
+          <t>1990-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1990-07</t>
+          <t>1990-06</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3361,7 +3416,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -3369,17 +3424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -3481,19 +3541,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1990-08-01</t>
+          <t>1990-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1990-08</t>
+          <t>1990-07</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="O16" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3517,7 +3577,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3525,17 +3585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3637,19 +3702,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1990-08-01</t>
+          <t>1990-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1990-08</t>
+          <t>1990-07</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="O17" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3751,7 +3816,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3759,17 +3824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3871,19 +3941,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1990-09-01</t>
+          <t>1990-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1990-09</t>
+          <t>1990-08</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3907,7 +3977,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3915,17 +3985,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4027,19 +4102,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1990-09-01</t>
+          <t>1990-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1990-09</t>
+          <t>1990-08</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4141,7 +4216,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4149,17 +4224,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4261,19 +4341,19 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1990-10-01</t>
+          <t>1990-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1990-10</t>
+          <t>1990-09</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4297,7 +4377,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -4305,17 +4385,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4417,19 +4502,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1990-10-01</t>
+          <t>1990-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1990-10</t>
+          <t>1990-09</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -4531,7 +4616,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4539,17 +4624,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4651,19 +4741,19 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1990-11-01</t>
+          <t>1990-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1990-11</t>
+          <t>1990-10</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4687,7 +4777,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4695,17 +4785,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4807,19 +4902,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1990-11-01</t>
+          <t>1990-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1990-11</t>
+          <t>1990-10</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -4921,7 +5016,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -4929,17 +5024,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -5041,19 +5141,19 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1990-12-01</t>
+          <t>1990-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1990-12</t>
+          <t>1990-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5077,7 +5177,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
@@ -5085,17 +5185,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS24" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5197,19 +5302,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1990-12-01</t>
+          <t>1990-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1990-12</t>
+          <t>1990-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5311,7 +5416,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -5319,17 +5424,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5431,19 +5541,19 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1990-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1990-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5467,7 +5577,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5475,17 +5585,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5587,19 +5702,19 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1990-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1991-01</t>
+          <t>1990-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5701,7 +5816,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5709,17 +5824,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5791,12 +5911,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5821,19 +5941,19 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1991-02-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1991-02</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>32</v>
+        <v>2033</v>
       </c>
       <c r="O28" t="n">
-        <v>32</v>
+        <v>2033</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5842,12 +5962,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5867,7 +5987,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5880,42 +6000,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5947,12 +6067,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5977,38 +6097,38 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1991-02-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1991-02</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>32</v>
+        <v>2033</v>
       </c>
       <c r="O29" t="n">
-        <v>32</v>
+        <v>2033</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -6018,12 +6138,12 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -6033,7 +6153,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6068,17 +6188,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6101,7 +6221,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -6114,42 +6234,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6211,19 +6331,19 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1991-03-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1991-03</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6247,7 +6367,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -6255,17 +6375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -6367,19 +6492,19 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1991-03-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1991-03</t>
+          <t>1991-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6481,7 +6606,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -6489,17 +6614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6601,19 +6731,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1991-04-01</t>
+          <t>1991-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1991-04</t>
+          <t>1991-02</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O32" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6637,7 +6767,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6645,17 +6775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6757,19 +6892,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1991-04-01</t>
+          <t>1991-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1991-04</t>
+          <t>1991-02</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O33" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -6871,7 +7006,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6879,17 +7014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -6991,19 +7131,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1991-05-01</t>
+          <t>1991-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1991-05</t>
+          <t>1991-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="O34" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7027,7 +7167,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -7035,17 +7175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -7147,19 +7292,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1991-05-01</t>
+          <t>1991-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1991-05</t>
+          <t>1991-03</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7261,7 +7406,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7269,17 +7414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -7381,19 +7531,19 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1991-06-01</t>
+          <t>1991-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1991-06</t>
+          <t>1991-04</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7417,7 +7567,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7425,17 +7575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7537,19 +7692,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1991-06-01</t>
+          <t>1991-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1991-06</t>
+          <t>1991-04</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -7651,7 +7806,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7659,17 +7814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7771,19 +7931,19 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1991-07-01</t>
+          <t>1991-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1991-07</t>
+          <t>1991-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="O38" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7807,7 +7967,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7815,17 +7975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -7927,19 +8092,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1991-07-01</t>
+          <t>1991-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1991-07</t>
+          <t>1991-05</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8041,7 +8206,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8049,17 +8214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8161,19 +8331,19 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>1991-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1991-08</t>
+          <t>1991-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="O40" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8197,7 +8367,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8205,17 +8375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -8317,19 +8492,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1991-08-01</t>
+          <t>1991-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1991-08</t>
+          <t>1991-06</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="O41" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8431,7 +8606,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8439,17 +8614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS41" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -8551,12 +8731,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1991-09-01</t>
+          <t>1991-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1991-09</t>
+          <t>1991-07</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -8587,7 +8767,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -8595,17 +8775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS42" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -8707,12 +8892,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1991-09-01</t>
+          <t>1991-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1991-09</t>
+          <t>1991-07</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -8821,7 +9006,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
@@ -8829,17 +9014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS43" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -8941,19 +9131,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1991-10-01</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1991-10</t>
+          <t>1991-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="O44" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8977,7 +9167,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8985,17 +9175,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9097,19 +9292,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1991-10-01</t>
+          <t>1991-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1991-10</t>
+          <t>1991-08</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="O45" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -9211,7 +9406,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9219,17 +9414,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9331,19 +9531,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1991-11-01</t>
+          <t>1991-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1991-11</t>
+          <t>1991-09</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="O46" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9367,7 +9567,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9375,17 +9575,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9487,19 +9692,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1991-11-01</t>
+          <t>1991-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1991-11</t>
+          <t>1991-09</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="O47" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -9601,7 +9806,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9609,17 +9814,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9721,19 +9931,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1991-12-01</t>
+          <t>1991-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1991-12</t>
+          <t>1991-10</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O48" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9757,7 +9967,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9765,17 +9975,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -9877,19 +10092,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1991-12-01</t>
+          <t>1991-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1991-12</t>
+          <t>1991-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O49" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9991,7 +10206,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9999,17 +10214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -10111,19 +10331,19 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1991-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1992-01</t>
+          <t>1991-11</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10147,7 +10367,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -10155,17 +10375,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -10267,19 +10492,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
+          <t>1991-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1992-01</t>
+          <t>1991-11</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -10381,7 +10606,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -10389,17 +10614,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -10501,19 +10731,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1992-02-01</t>
+          <t>1991-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1992-02</t>
+          <t>1991-12</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="O52" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10537,7 +10767,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10545,17 +10775,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10657,19 +10892,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1992-02-01</t>
+          <t>1991-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1992-02</t>
+          <t>1991-12</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="O53" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -10771,7 +11006,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10779,17 +11014,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10861,12 +11101,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10891,19 +11131,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1992-03-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1992-03</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>11</v>
+        <v>2118</v>
       </c>
       <c r="O54" t="n">
-        <v>11</v>
+        <v>2118</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10912,12 +11152,12 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -10937,7 +11177,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -10950,42 +11190,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11257,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11047,38 +11287,38 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>1992-03-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>1992-03</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>11</v>
+        <v>2118</v>
       </c>
       <c r="O55" t="n">
-        <v>11</v>
+        <v>2118</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11088,12 +11328,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -11103,7 +11343,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11138,17 +11378,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11171,7 +11411,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11184,42 +11424,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11281,19 +11521,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1992-04-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1992-04</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11317,7 +11557,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11325,17 +11565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -11437,19 +11682,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1992-04-01</t>
+          <t>1992-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1992-04</t>
+          <t>1992-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11551,7 +11796,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11559,17 +11804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -11671,19 +11921,19 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>1992-05-01</t>
+          <t>1992-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1992-05</t>
+          <t>1992-02</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="O58" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11707,7 +11957,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11715,17 +11965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11827,19 +12082,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1992-05-01</t>
+          <t>1992-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1992-05</t>
+          <t>1992-02</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="O59" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -11941,7 +12196,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -11949,17 +12204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -12061,19 +12321,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1992-06-01</t>
+          <t>1992-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1992-06</t>
+          <t>1992-03</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O60" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12097,7 +12357,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12105,17 +12365,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12217,19 +12482,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1992-06-01</t>
+          <t>1992-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1992-06</t>
+          <t>1992-03</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O61" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12331,7 +12596,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12339,17 +12604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12451,12 +12721,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1992-07-01</t>
+          <t>1992-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1992-07</t>
+          <t>1992-04</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -12487,7 +12757,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12495,17 +12765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12607,12 +12882,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1992-07-01</t>
+          <t>1992-04-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1992-07</t>
+          <t>1992-04</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -12721,7 +12996,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12729,17 +13004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -12841,19 +13121,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1992-08-01</t>
+          <t>1992-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1992-08</t>
+          <t>1992-05</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="O64" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12877,7 +13157,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12885,17 +13165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -12997,19 +13282,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1992-08-01</t>
+          <t>1992-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>1992-08</t>
+          <t>1992-05</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="O65" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13111,7 +13396,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13119,17 +13404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13231,19 +13521,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1992-09-01</t>
+          <t>1992-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1992-09</t>
+          <t>1992-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13267,7 +13557,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13275,17 +13565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13387,19 +13682,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1992-09-01</t>
+          <t>1992-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>1992-09</t>
+          <t>1992-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O67" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13501,7 +13796,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13509,17 +13804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13621,19 +13921,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>1992-10-01</t>
+          <t>1992-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>1992-10</t>
+          <t>1992-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O68" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13657,7 +13957,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13665,17 +13965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13777,19 +14082,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1992-10-01</t>
+          <t>1992-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>1992-10</t>
+          <t>1992-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O69" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -13891,7 +14196,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -13899,17 +14204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -14011,19 +14321,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>1992-11-01</t>
+          <t>1992-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1992-11</t>
+          <t>1992-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O70" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14047,7 +14357,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14055,17 +14365,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14167,19 +14482,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1992-11-01</t>
+          <t>1992-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>1992-11</t>
+          <t>1992-08</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O71" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -14281,7 +14596,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14289,17 +14604,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14401,19 +14721,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1992-12-01</t>
+          <t>1992-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>1992-12</t>
+          <t>1992-09</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O72" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14437,7 +14757,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -14445,17 +14765,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS72" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -14557,19 +14882,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1992-12-01</t>
+          <t>1992-09-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1992-12</t>
+          <t>1992-09</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O73" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -14671,7 +14996,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
@@ -14679,17 +15004,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS73" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -14791,19 +15121,19 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1992-10-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1993-01</t>
+          <t>1992-10</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O74" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -14827,7 +15157,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
@@ -14835,17 +15165,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS74" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -14947,19 +15282,19 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1992-10-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>1993-01</t>
+          <t>1992-10</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O75" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15061,7 +15396,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
@@ -15069,17 +15404,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS75" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -15181,19 +15521,19 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1993-02-01</t>
+          <t>1992-11-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1993-02</t>
+          <t>1992-11</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O76" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15217,7 +15557,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15225,17 +15565,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -15337,19 +15682,19 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1993-02-01</t>
+          <t>1992-11-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>1993-02</t>
+          <t>1992-11</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O77" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15451,7 +15796,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -15459,17 +15804,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -15571,19 +15921,19 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1993-03-01</t>
+          <t>1992-12-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1993-03</t>
+          <t>1992-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O78" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15607,7 +15957,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
@@ -15615,17 +15965,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS78" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -15727,19 +16082,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1993-03-01</t>
+          <t>1992-12-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1993-03</t>
+          <t>1992-12</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O79" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -15841,7 +16196,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
@@ -15849,17 +16204,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS79" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -15931,12 +16291,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15961,19 +16321,19 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1993-04-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>1993-04</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>10</v>
+        <v>2053</v>
       </c>
       <c r="O80" t="n">
-        <v>10</v>
+        <v>2053</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -15982,12 +16342,12 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -16007,7 +16367,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT80" t="n">
@@ -16020,42 +16380,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16087,12 +16447,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -16117,38 +16477,38 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1993-04-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>1993-04</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>10</v>
+        <v>2053</v>
       </c>
       <c r="O81" t="n">
-        <v>10</v>
+        <v>2053</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -16158,12 +16518,12 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -16173,7 +16533,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -16208,17 +16568,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16241,7 +16601,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT81" t="n">
@@ -16254,42 +16614,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16351,19 +16711,19 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1993-05-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1993-05</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="O82" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16387,7 +16747,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -16395,17 +16755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -16507,19 +16872,19 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1993-05-01</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>1993-05</t>
+          <t>1993-01</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="O83" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -16621,7 +16986,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -16629,17 +16994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -16741,19 +17111,19 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>1993-06-01</t>
+          <t>1993-02-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>1993-06</t>
+          <t>1993-02</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16777,7 +17147,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -16785,17 +17155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -16897,19 +17272,19 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1993-06-01</t>
+          <t>1993-02-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>1993-06</t>
+          <t>1993-02</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17011,7 +17386,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -17019,17 +17394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -17131,19 +17511,19 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1993-07-01</t>
+          <t>1993-03-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>1993-07</t>
+          <t>1993-03</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17167,7 +17547,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -17175,17 +17555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -17287,19 +17672,19 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1993-07-01</t>
+          <t>1993-03-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>1993-07</t>
+          <t>1993-03</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -17401,7 +17786,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -17409,17 +17794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -17521,19 +17911,19 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1993-08-01</t>
+          <t>1993-04-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>1993-08</t>
+          <t>1993-04</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="O88" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17557,7 +17947,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -17565,17 +17955,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -17677,19 +18072,19 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1993-08-01</t>
+          <t>1993-04-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>1993-08</t>
+          <t>1993-04</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="O89" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -17791,7 +18186,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -17799,17 +18194,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -17911,19 +18311,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>1993-09-01</t>
+          <t>1993-05-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>1993-09</t>
+          <t>1993-05</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="O90" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -17947,7 +18347,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -17955,17 +18355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -18067,19 +18472,19 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1993-09-01</t>
+          <t>1993-05-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>1993-09</t>
+          <t>1993-05</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="O91" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -18181,7 +18586,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -18189,17 +18594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -18301,19 +18711,19 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>1993-10-01</t>
+          <t>1993-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>1993-10</t>
+          <t>1993-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O92" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18337,7 +18747,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -18345,17 +18755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS92" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -18457,19 +18872,19 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>1993-10-01</t>
+          <t>1993-06-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>1993-10</t>
+          <t>1993-06</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O93" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18571,7 +18986,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
@@ -18579,17 +18994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS93" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -18691,19 +19111,19 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>1993-11-01</t>
+          <t>1993-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>1993-11</t>
+          <t>1993-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="O94" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18727,7 +19147,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -18735,17 +19155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS94" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -18847,19 +19272,19 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>1993-11-01</t>
+          <t>1993-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>1993-11</t>
+          <t>1993-07</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="O95" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18961,7 +19386,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -18969,17 +19394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS95" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -19081,19 +19511,19 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1993-12-01</t>
+          <t>1993-08-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>1993-12</t>
+          <t>1993-08</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O96" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19117,7 +19547,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -19125,17 +19555,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -19237,19 +19672,19 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>1993-12-01</t>
+          <t>1993-08-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>1993-12</t>
+          <t>1993-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O97" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -19351,7 +19786,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -19359,17 +19794,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -19471,19 +19911,19 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1993-09-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1993-09</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O98" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19507,7 +19947,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
@@ -19515,17 +19955,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS98" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -19627,19 +20072,19 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1993-09-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>1994-01</t>
+          <t>1993-09</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O99" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -19741,7 +20186,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
@@ -19749,17 +20194,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS99" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -19861,19 +20311,19 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1994-02-01</t>
+          <t>1993-10-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>1994-02</t>
+          <t>1993-10</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="O100" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -19897,7 +20347,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
@@ -19905,17 +20355,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS100" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -20017,19 +20472,19 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>1994-02-01</t>
+          <t>1993-10-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>1994-02</t>
+          <t>1993-10</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="O101" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -20131,7 +20586,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
@@ -20139,17 +20594,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS101" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -20251,19 +20711,19 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1994-03-01</t>
+          <t>1993-11-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>1994-03</t>
+          <t>1993-11</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="O102" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20287,7 +20747,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -20295,17 +20755,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -20407,19 +20872,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1994-03-01</t>
+          <t>1993-11-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>1994-03</t>
+          <t>1993-11</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="O103" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20521,7 +20986,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -20529,17 +20994,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -20641,19 +21111,19 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>1994-04-01</t>
+          <t>1993-12-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>1994-04</t>
+          <t>1993-12</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O104" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20677,7 +21147,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -20685,17 +21155,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -20797,19 +21272,19 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1994-04-01</t>
+          <t>1993-12-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>1994-04</t>
+          <t>1993-12</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O105" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -20911,7 +21386,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -20919,17 +21394,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -21001,12 +21481,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21031,19 +21511,19 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>1994-05-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>1994-05</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>32</v>
+        <v>2106</v>
       </c>
       <c r="O106" t="n">
-        <v>32</v>
+        <v>2106</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21052,12 +21532,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -21077,7 +21557,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21090,42 +21570,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21157,12 +21637,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -21187,38 +21667,38 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>1994-05-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1994-05</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>32</v>
+        <v>2106</v>
       </c>
       <c r="O107" t="n">
-        <v>32</v>
+        <v>2106</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -21228,12 +21708,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -21243,7 +21723,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -21278,17 +21758,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21311,7 +21791,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_CA_PHAC_CNDSS_D119_ANNUAL</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -21324,42 +21804,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21421,19 +21901,19 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>1994-06-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>1994-06</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21457,7 +21937,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
@@ -21465,17 +21945,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS108" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -21577,19 +22062,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>1994-06-01</t>
+          <t>1994-01-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>1994-06</t>
+          <t>1994-01</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
@@ -21691,7 +22176,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -21699,17 +22184,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -21811,19 +22301,19 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>1994-07-01</t>
+          <t>1994-02-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>1994-07</t>
+          <t>1994-02</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O110" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21847,7 +22337,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -21855,17 +22345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -21967,19 +22462,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>1994-07-01</t>
+          <t>1994-02-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>1994-07</t>
+          <t>1994-02</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O111" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -22081,7 +22576,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
@@ -22089,17 +22584,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS111" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -22201,19 +22701,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>1994-03-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>1994-08</t>
+          <t>1994-03</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O112" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22237,7 +22737,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -22245,17 +22745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS112" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -22357,19 +22862,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>1994-03-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>1994-08</t>
+          <t>1994-03</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O113" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -22471,7 +22976,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
@@ -22479,17 +22984,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS113" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -22591,19 +23101,19 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>1994-09-01</t>
+          <t>1994-04-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>1994-09</t>
+          <t>1994-04</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22627,7 +23137,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
@@ -22635,17 +23145,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS114" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -22747,19 +23262,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>1994-09-01</t>
+          <t>1994-04-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>1994-09</t>
+          <t>1994-04</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -22861,7 +23376,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
@@ -22869,17 +23384,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS115" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -22981,19 +23501,19 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>1994-10-01</t>
+          <t>1994-05-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>1994-10</t>
+          <t>1994-05</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="O116" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -23017,7 +23537,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
@@ -23025,17 +23545,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS116" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -23137,19 +23662,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1994-10-01</t>
+          <t>1994-05-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>1994-10</t>
+          <t>1994-05</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="O117" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -23251,7 +23776,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -23259,17 +23784,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -23371,19 +23901,19 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>1994-11-01</t>
+          <t>1994-06-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>1994-11</t>
+          <t>1994-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O118" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23407,7 +23937,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -23415,17 +23945,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS118" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -23527,19 +24062,19 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>1994-11-01</t>
+          <t>1994-06-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>1994-11</t>
+          <t>1994-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O119" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23641,7 +24176,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -23649,17 +24184,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS119" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -23761,19 +24301,19 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>1994-12-01</t>
+          <t>1994-07-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>1994-12</t>
+          <t>1994-07</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O120" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23797,7 +24337,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -23805,17 +24345,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -23917,19 +24462,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>1994-12-01</t>
+          <t>1994-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>1994-12</t>
+          <t>1994-07</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O121" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24031,7 +24576,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -24039,55 +24584,2060 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>1994-08-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>1994-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>29</v>
+      </c>
+      <c r="O122" t="n">
+        <v>29</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>1994-08-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>1994-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>29</v>
+      </c>
+      <c r="O123" t="n">
+        <v>29</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
         <v>1</v>
       </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV121" t="inlineStr">
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW121" t="inlineStr">
+      <c r="AW123" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY121" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA121" t="inlineStr">
+      <c r="BA123" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB121" t="inlineStr">
+      <c r="BB123" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC121" t="inlineStr">
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>1994-09-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>1994-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>15</v>
+      </c>
+      <c r="O124" t="n">
+        <v>15</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>1994-09-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1994-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>15</v>
+      </c>
+      <c r="O125" t="n">
+        <v>15</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>1994-10-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>1994-10</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>11</v>
+      </c>
+      <c r="O126" t="n">
+        <v>11</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>1994-10-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>1994-10</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>11</v>
+      </c>
+      <c r="O127" t="n">
+        <v>11</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>1994-11-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>1994-11</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>30</v>
+      </c>
+      <c r="O128" t="n">
+        <v>30</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>1994-11-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>1994-11</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>30</v>
+      </c>
+      <c r="O129" t="n">
+        <v>30</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>1994-12-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>1994-12</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>15</v>
+      </c>
+      <c r="O130" t="n">
+        <v>15</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>1994-12-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>1994-12</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>15</v>
+      </c>
+      <c r="O131" t="n">
+        <v>15</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -24209,7 +26759,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -24219,7 +26769,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -24239,7 +26789,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -24249,7 +26799,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -24271,7 +26821,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1308</v>
+        <v>11632</v>
       </c>
     </row>
     <row r="16">
